--- a/reports/2026-10-17/private_scholarships_report_2026-10-17.xlsx
+++ b/reports/2026-10-17/private_scholarships_report_2026-10-17.xlsx
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 07:40 PKT</t>
+          <t>2026-10-17 07:59 PKT</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUN-20261017-074058</t>
+          <t>RUN-20261017-075906</t>
         </is>
       </c>
     </row>

--- a/reports/2026-10-17/private_scholarships_report_2026-10-17.xlsx
+++ b/reports/2026-10-17/private_scholarships_report_2026-10-17.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Report Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active Opportunities'!$A$1:$R$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority Highlights'!$A$1:$R$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active Opportunities'!$A$1:$R$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority Highlights'!$A$1:$R$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'International'!$A$1:$R$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Watchlist (Awaiting Call)'!$A$1:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Watchlist (Awaiting Call)'!$A$1:$R$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -604,7 +604,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0003</t>
+          <t>SCH-202610-0072</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -694,38 +694,36 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0018</t>
+          <t>SCH-202610-0009</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
+          <t>Rehmatul Lil Alameen Scholarship for Dini Madaris 2026 (رحمت اللعالمین ﷺ اسکالرشپ برائے دینی مدارس)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Government of Pakistan</t>
+          <t>Auqaf, Hajj, Religious &amp; Minority Affairs Department</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>federal govt</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
+          <t>2027-03-25</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>159</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -744,22 +742,22 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 100,000</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>Registered Dini Madaris of Khyber Pakhtunkhwa</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>MS and PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>Merit-based</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -769,7 +767,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>https://eportal.hec.gov.pk/idps75</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -779,7 +777,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
+          <t>https://scholarships.kpitb.online/#laptopScheme</t>
         </is>
       </c>
     </row>
@@ -791,12 +789,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CM Foreign Scholarship</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -804,29 +802,27 @@
           <t>provincial govt</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -836,12 +832,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 60,000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>University of Swabi</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -851,7 +847,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Need-based</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -861,7 +857,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -871,29 +867,29 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://scholarships.kpitb.online/#laptopScheme</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0017</t>
+          <t>SCH-202610-0079</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister Foreign Scholarship Program</t>
+          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister of Khyber Pakhtunkhwa through Khyber Pakhtunkhwa Education Foundation</t>
+          <t>Government of Pakistan</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
+          <t>federal govt</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -933,17 +929,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>selected universities in the People's Republic of China</t>
+          <t>world's top 25 ranked universities</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+          <t>MS and PhD</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>merit cum in-affordability basis</t>
+          <t>world's top 25 ranked universities</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -953,7 +949,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>https://eportal.hec.gov.pk/idps75</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -963,19 +959,19 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0009</t>
+          <t>SCH-202610-0075</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KP Youth Scholarship</t>
+          <t>CM Foreign Scholarship</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1025,7 +1021,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1035,7 +1031,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>good academic merit</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1045,7 +1041,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1067,92 +1063,736 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HEC Need Based Scholarships</t>
+          <t>Chief Minister Foreign Scholarship Program</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Higher Education Commission, Islamabad / Government of Pakistan</t>
+          <t>Government of Khyber Pakhtunkhwa / Khyber Pakhtunkhwa Education Foundation</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>selected universities in the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>merit cum in-affordability basis</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0060</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Girls Stipend Programme</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 4,500</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>80% attendance</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0067</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>HEC Internation National Scholarships</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>federal govt</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Deadline not stated</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/InternationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0066</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>HEC National Scholarships</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/NationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0059</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Rehmat Ul Lil Alamin</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>participating public sector Universities/Institutions and their campuses which are receiving annual recurring grant through Higher Education Commission, Islamabad</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>talented students</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/NBS/Pages/default.aspx</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 50,000</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/NBS/Pages/default.aspx</t>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0058</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Stoori Da Pakhtunkhwa Program</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 15,000</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Top twenty position holders of Government Schools in SSC and HSSC exams</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0057</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Talented Student through ETEA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 380,000</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>ETEA test</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0063</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Foundation Excellence</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 350,000</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>ETEA test</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R7"/>
+  <autoFilter ref="A1:R14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1163,7 +1803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1281,7 +1921,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0003</t>
+          <t>SCH-202610-0072</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1371,38 +2011,36 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0018</t>
+          <t>SCH-202610-0009</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
+          <t>Rehmatul Lil Alameen Scholarship for Dini Madaris 2026 (رحمت اللعالمین ﷺ اسکالرشپ برائے دینی مدارس)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Government of Pakistan</t>
+          <t>Auqaf, Hajj, Religious &amp; Minority Affairs Department</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>federal govt</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
+          <t>2027-03-25</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>159</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -1421,22 +2059,22 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 100,000</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>Registered Dini Madaris of Khyber Pakhtunkhwa</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>MS and PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>Merit-based</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -1446,7 +2084,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>https://eportal.hec.gov.pk/idps75</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -1456,29 +2094,29 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
+          <t>https://scholarships.kpitb.online/#laptopScheme</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0008</t>
+          <t>SCH-202610-0079</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CM Foreign Scholarship</t>
+          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>Government of Pakistan</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
+          <t>federal govt</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1518,17 +2156,17 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>world's top 25 ranked universities</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>MS and PhD</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>world's top 25 ranked universities</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -1538,7 +2176,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>https://eportal.hec.gov.pk/idps75</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1548,24 +2186,24 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0017</t>
+          <t>SCH-202610-0075</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister Foreign Scholarship Program</t>
+          <t>CM Foreign Scholarship</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister of Khyber Pakhtunkhwa through Khyber Pakhtunkhwa Education Foundation</t>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1610,17 +2248,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>selected universities in the People's Republic of China</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>merit cum in-affordability basis</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1630,7 +2268,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1640,24 +2278,24 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>https://ef.kp.gov.pk/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0009</t>
+          <t>SCH-202610-0006</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KP Youth Scholarship</t>
+          <t>Chief Minister Foreign Scholarship Program</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>Government of Khyber Pakhtunkhwa / Khyber Pakhtunkhwa Education Foundation</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1702,17 +2340,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+          <t>selected universities in the People's Republic of China</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>good academic merit</t>
+          <t>merit cum in-affordability basis</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1722,7 +2360,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1732,12 +2370,564 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0060</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Girls Stipend Programme</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 4,500</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>80% attendance</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0067</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>HEC Internation National Scholarships</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/InternationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0066</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>HEC National Scholarships</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/NationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0059</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Rehmat Ul Lil Alamin</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 50,000</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0058</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Stoori Da Pakhtunkhwa Program</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 15,000</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Top twenty position holders of Government Schools in SSC and HSSC exams</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0057</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Talented Student through ETEA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 380,000</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>ETEA test</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R6"/>
+  <autoFilter ref="A1:R12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1866,7 +3056,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0016</t>
+          <t>SCH-202610-0078</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1967,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2082,8 +3272,190 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0013</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>U.S. - Pakistan Professional Partnership Program for Journalists</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>United States Educational Foundation in Pakistan</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Previous cycle – awaiting new call</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-2280</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Currently working as a journalist with three to ten years of active experience in journalism with any media organization</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/journalism.cfm</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/journalism.cfm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0068</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Community College Initiative Program (CCIP)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>United States Educational Foundation in Pakistan (USEFP)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Previous cycle – awaiting new call</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>November 20, 2019</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>accredited U.S. community colleges</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>non-degree study (vocational certificate)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>English language proficiency, potential to have a positive impact on Pakistan's future development and demonstrated leadership</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/ccip.cfm</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/ccip.cfm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R2"/>
+  <autoFilter ref="A1:R3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2133,7 +3505,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 07:59 PKT</t>
+          <t>2026-10-17 08:21 PKT</t>
         </is>
       </c>
     </row>
@@ -2145,7 +3517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUN-20261017-075906</t>
+          <t>RUN-20261017-082108</t>
         </is>
       </c>
     </row>
@@ -2156,7 +3528,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2166,7 +3538,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2176,7 +3548,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2196,7 +3568,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2206,7 +3578,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -2227,7 +3599,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
